--- a/r-code/18.3 software-dictionary.xlsx
+++ b/r-code/18.3 software-dictionary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\64204\Desktop\master\r-code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{700C6BB6-7E21-4C47-81E3-4DB7314F2055}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CE3532A-B195-4980-A89D-F8BDAD583F25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="30">
   <si>
     <t>Type</t>
   </si>
@@ -106,6 +106,15 @@
   </si>
   <si>
     <t>Publication-ready plots. But really just some useful stats for ggplot</t>
+  </si>
+  <si>
+    <t>patchwork</t>
+  </si>
+  <si>
+    <t>1.2.0</t>
+  </si>
+  <si>
+    <t>Plot facetting</t>
   </si>
 </sst>
 </file>
@@ -423,7 +432,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.42578125" customWidth="1"/>
@@ -538,6 +547,20 @@
         <v>26</v>
       </c>
     </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" t="s">
+        <v>29</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
